--- a/artfynd/A 17144-2023 artfynd.xlsx
+++ b/artfynd/A 17144-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17144-2023 artfynd.xlsx
+++ b/artfynd/A 17144-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2533,6 +2533,1125 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115045812</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>563455</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6576284</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca trettio plantor 12 meter utanför Holmen skog AB s avgränsningar för knärot.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115046047</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>563451</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6576290</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>20 knärot 15 m utanför Holmens skogs avgränsningar för växtplatser knärot.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115049847</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>563446</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6576328</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115073086</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>563487</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6576004</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Två plantor under senvuxen gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115075254</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>563437</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6575993</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115077038</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>563470</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6575978</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115074228</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>563458</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6575996</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>115073720</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>563478</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6576025</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>115074041</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>563472</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6575994</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17144-2023 artfynd.xlsx
+++ b/artfynd/A 17144-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3652,6 +3652,384 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115072528</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>563481</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6575990</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>115072782</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>563483</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6575995</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Tvåhundra knärotsplantor inom yta av 5 kvm. Skogen är avverkningsanmäld. Ingen avgränsning eller skyddszon.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115072402</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>563457</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6575978</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växer bredvid en nedsågad senvuxen gran i skuggigt läge. Skogen avverkningsanmäld.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17144-2023 artfynd.xlsx
+++ b/artfynd/A 17144-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,7 +2913,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115073086</v>
+        <v>115049721</v>
       </c>
       <c r="B20" t="n">
         <v>97558</v>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563487</v>
+        <v>563452</v>
       </c>
       <c r="R20" t="n">
-        <v>6576004</v>
+        <v>6576326</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2995,27 +2995,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Två plantor under senvuxen gran.</t>
+          <t>Holmen planerar avverka en knärotsskog. De här plantorna har inte avgränsats.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3042,7 +3042,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115075254</v>
+        <v>115049490</v>
       </c>
       <c r="B21" t="n">
         <v>97558</v>
@@ -3077,14 +3077,10 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3094,13 +3090,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563437</v>
+        <v>563450</v>
       </c>
       <c r="R21" t="n">
-        <v>6575993</v>
+        <v>6576270</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3124,22 +3120,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3166,7 +3162,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115077038</v>
+        <v>115073086</v>
       </c>
       <c r="B22" t="n">
         <v>97558</v>
@@ -3201,10 +3197,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563470</v>
+        <v>563487</v>
       </c>
       <c r="R22" t="n">
-        <v>6575978</v>
+        <v>6576004</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3259,7 +3259,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två plantor under senvuxen gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3286,7 +3291,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115074228</v>
+        <v>115075254</v>
       </c>
       <c r="B23" t="n">
         <v>97558</v>
@@ -3321,7 +3326,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3338,13 +3343,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563458</v>
+        <v>563437</v>
       </c>
       <c r="R23" t="n">
-        <v>6575996</v>
+        <v>6575993</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3383,7 +3388,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3410,7 +3415,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115073720</v>
+        <v>115077038</v>
       </c>
       <c r="B24" t="n">
         <v>97558</v>
@@ -3445,7 +3450,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3458,13 +3463,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563478</v>
+        <v>563470</v>
       </c>
       <c r="R24" t="n">
-        <v>6576025</v>
+        <v>6575978</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3493,7 +3498,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3503,7 +3508,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3530,7 +3535,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115074041</v>
+        <v>115074228</v>
       </c>
       <c r="B25" t="n">
         <v>97558</v>
@@ -3565,7 +3570,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3582,13 +3587,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563472</v>
+        <v>563458</v>
       </c>
       <c r="R25" t="n">
-        <v>6575994</v>
+        <v>6575996</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3617,7 +3622,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3627,7 +3632,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3654,7 +3659,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115072528</v>
+        <v>115073720</v>
       </c>
       <c r="B26" t="n">
         <v>97558</v>
@@ -3689,7 +3694,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3702,13 +3707,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563481</v>
+        <v>563478</v>
       </c>
       <c r="R26" t="n">
-        <v>6575990</v>
+        <v>6576025</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3737,7 +3742,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3747,7 +3752,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3774,7 +3779,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115072782</v>
+        <v>115074041</v>
       </c>
       <c r="B27" t="n">
         <v>97558</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3826,13 +3831,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563483</v>
+        <v>563472</v>
       </c>
       <c r="R27" t="n">
-        <v>6575995</v>
+        <v>6575994</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3861,7 +3866,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3871,12 +3876,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Tvåhundra knärotsplantor inom yta av 5 kvm. Skogen är avverkningsanmäld. Ingen avgränsning eller skyddszon.</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3903,7 +3903,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115072402</v>
+        <v>115072528</v>
       </c>
       <c r="B28" t="n">
         <v>97558</v>
@@ -3938,14 +3938,10 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3955,10 +3951,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563457</v>
+        <v>563481</v>
       </c>
       <c r="R28" t="n">
-        <v>6575978</v>
+        <v>6575990</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3990,7 +3986,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4000,12 +3996,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växer bredvid en nedsågad senvuxen gran i skuggigt läge. Skogen avverkningsanmäld.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4029,6 +4020,1018 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>115072782</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>563483</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6575995</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Tvåhundra knärotsplantor inom yta av 5 kvm. Skogen är avverkningsanmäld. Ingen avgränsning eller skyddszon.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115072402</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>563457</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6575978</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer bredvid en nedsågad senvuxen gran i skuggigt läge. Skogen avverkningsanmäld.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115124786</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>563456</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6576135</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>115125738</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>563449</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6576003</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Knäroten växer alldeles intill stigen ”Björnlunken”. Ett motionsspår.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>115125073</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>563462</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6576127</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>115123774</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>563458</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6576010</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>115125472</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>563446</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6576095</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>115124188</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>563480</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6576026</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Trettio plantor i mossan och en med vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17144-2023 artfynd.xlsx
+++ b/artfynd/A 17144-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96209026</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563446.4798573141</v>
+        <v>563447</v>
       </c>
       <c r="R2" t="n">
-        <v>6576087.792096522</v>
+        <v>6576088</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,60 +780,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96379879</v>
+        <v>104094718</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Köpingsåsen, Srm</t>
+          <t>Haglunda, Masten/grustaget O Gräshagen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563297.0507497852</v>
+        <v>563406</v>
       </c>
       <c r="R3" t="n">
-        <v>6576461.021573178</v>
+        <v>6575946</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer på mager tallmark med inslag av gran nära ett gammalt grustag.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,88 +885,86 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallhed med inslag av gran.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108533341</v>
+        <v>112079423</v>
       </c>
       <c r="B4" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563469.0179328058</v>
+        <v>563404</v>
       </c>
       <c r="R4" t="n">
-        <v>6576482.784237958</v>
+        <v>6575955</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,27 +988,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tallåga i fuktig blåbärsbarrskog</t>
+          <t>en ring med 0,8 m i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,78 +1013,73 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108535141</v>
+        <v>112079424</v>
       </c>
       <c r="B5" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>3100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563437.3419033252</v>
+        <v>563412</v>
       </c>
       <c r="R5" t="n">
-        <v>6576175.448365967</v>
+        <v>6575951</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1103,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>tre ringar om vardera ca 1 m i diameter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,77 +1128,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108534864</v>
+        <v>96206087</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Söder om Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563450.267524792</v>
+        <v>563365</v>
       </c>
       <c r="R6" t="n">
-        <v>6576197.616636516</v>
+        <v>6576426</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,27 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Utspridda plantor bland blåbärsriset. Fin blåbärsbarrskog</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,74 +1230,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108534315</v>
+        <v>112079434</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563439.3773023786</v>
+        <v>563374</v>
       </c>
       <c r="R7" t="n">
-        <v>6576206.623561237</v>
+        <v>6575970</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1384,27 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Friska knärotsplantor i fuktig blåbärsbarrskog. Sandås. Avverkningsanmäld skog.</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,74 +1331,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108677391</v>
+        <v>112079438</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563440.3319756779</v>
+        <v>563353</v>
       </c>
       <c r="R8" t="n">
-        <v>6576424.620375446</v>
+        <v>6576435</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1513,27 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>19:28</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En planta, kanske flera i mossan. Sandtallskog.</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,77 +1432,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108675609</v>
+        <v>96209215</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Söder om Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563469.0108007342</v>
+        <v>563498</v>
       </c>
       <c r="R9" t="n">
-        <v>6576452.666180359</v>
+        <v>6576515</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1642,27 +1514,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:40</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 15 knärotsplantor växer under en samling senvuxna granar. Sandtallskog.</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,77 +1534,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108678257</v>
+        <v>96379933</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563442.2973743116</v>
+        <v>563311</v>
       </c>
       <c r="R10" t="n">
-        <v>6576276.611429942</v>
+        <v>6576403</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1771,27 +1616,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19:52</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer under en samling senvuxna granar. Sandtallskog.</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,77 +1636,75 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108676184</v>
+        <v>104067617</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Haglunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563449.0460401183</v>
+        <v>563395</v>
       </c>
       <c r="R11" t="n">
-        <v>6576484.49180426</v>
+        <v>6575949</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1900,27 +1728,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tre knärotsplantor i sandtallskog.</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,62 +1770,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108678905</v>
+        <v>112079418</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563435.3362554276</v>
+        <v>563454</v>
       </c>
       <c r="R12" t="n">
-        <v>6576264.753455259</v>
+        <v>6575956</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2029,27 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>20:05</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 80 plantor, troligen mer. Fuktig del av sandtallskog, med en samling senvuxna granar.</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2064,73 +1855,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108535895</v>
+        <v>112079433</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västerdal, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563461.0664137939</v>
+        <v>563374</v>
       </c>
       <c r="R13" t="n">
-        <v>6576132.962094987</v>
+        <v>6575970</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2154,27 +1936,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Många hundratals plantor utspridda längs ett stråk om ca 50m. Underröjning har skett inför planerad avverkning. Fin fuktig barrblandskog</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2189,27 +1956,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111379535</v>
+        <v>112079439</v>
       </c>
       <c r="B14" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,47 +1983,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Masten/grustaget O Gräshagen (Masten/grustaget O Gräshagen), Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563458.5748727873</v>
+        <v>563408</v>
       </c>
       <c r="R14" t="n">
-        <v>6576006.820268428</v>
+        <v>6576469</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2281,22 +2037,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:17</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:17</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2311,27 +2057,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112079417</v>
+        <v>111379535</v>
       </c>
       <c r="B15" t="n">
-        <v>8387</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2339,37 +2084,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Köpingsåsen, Srm</t>
+          <t>Masten/grustaget O Gräshagen, Masten/grustaget O Gräshagen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563452</v>
+        <v>563459</v>
       </c>
       <c r="R15" t="n">
-        <v>6576051</v>
+        <v>6576007</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2393,12 +2148,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2413,69 +2178,67 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112079439</v>
+        <v>96379879</v>
       </c>
       <c r="B16" t="n">
-        <v>90872</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563408</v>
+        <v>563297</v>
       </c>
       <c r="R16" t="n">
-        <v>6576469</v>
+        <v>6576461</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2499,12 +2262,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2519,12 +2282,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2535,65 +2298,61 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115045812</v>
+        <v>108533341</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563455</v>
+        <v>563468</v>
       </c>
       <c r="R17" t="n">
-        <v>6576283</v>
+        <v>6576483</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2617,27 +2376,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca trettio plantor 12 meter utanför Holmen skog AB s avgränsningar för knärot.</t>
+          <t>På tallåga i fuktig blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2664,61 +2423,61 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115049490</v>
+        <v>108535141</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563449</v>
+        <v>563438</v>
       </c>
       <c r="R18" t="n">
-        <v>6576270</v>
+        <v>6576176</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2742,22 +2501,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2784,65 +2543,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115046047</v>
+        <v>108692909</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Tallskogen N Segersta, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563451</v>
+        <v>563430</v>
       </c>
       <c r="R19" t="n">
-        <v>6576290</v>
+        <v>6576359</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2866,27 +2617,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>20 knärot 15 m utanför Holmens skogs avgränsningar för växtplatser knärot.</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2895,8 +2641,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2913,65 +2685,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115049721</v>
+        <v>112079417</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Köpingsåsen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>563452</v>
       </c>
       <c r="R20" t="n">
-        <v>6576326</v>
+        <v>6576051</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2995,27 +2750,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Holmen planerar avverka en knärotsskog. De här plantorna har inte avgränsats.</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3030,27 +2770,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115049847</v>
+        <v>108534315</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3077,26 +2816,30 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563446</v>
+        <v>563439</v>
       </c>
       <c r="R21" t="n">
-        <v>6576328</v>
+        <v>6576207</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3120,22 +2863,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Friska knärotsplantor i fuktig blåbärsbarrskog. Sandås. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3162,15 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115074041</v>
+        <v>108534864</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,7 +2940,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3210,14 +2953,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563472</v>
+        <v>563451</v>
       </c>
       <c r="R22" t="n">
-        <v>6575994</v>
+        <v>6576198</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3244,22 +2987,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Utspridda plantor bland blåbärsriset. Fin blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3286,15 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115075254</v>
+        <v>108535011</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3321,27 +3064,23 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563436</v>
+        <v>563428</v>
       </c>
       <c r="R23" t="n">
-        <v>6575993</v>
+        <v>6576219</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3368,22 +3107,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3410,15 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115072402</v>
+        <v>108535895</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3443,11 +3177,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3458,17 +3188,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563457</v>
+        <v>563461</v>
       </c>
       <c r="R24" t="n">
-        <v>6575978</v>
+        <v>6576132</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3492,27 +3222,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer bredvid en nedsågad senvuxen gran i skuggigt läge. Skogen avverkningsanmäld.</t>
+          <t>Många hundratals plantor utspridda längs ett stråk om ca 50m. Underröjning har skett inför planerad avverkning. Fin fuktig barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,15 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115074228</v>
+        <v>108675609</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3574,7 +3299,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3587,17 +3312,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563458</v>
+        <v>563470</v>
       </c>
       <c r="R25" t="n">
-        <v>6575996</v>
+        <v>6576453</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3621,22 +3346,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ca 15 knärotsplantor växer under en samling senvuxna granar. Sandtallskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3663,15 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115072782</v>
+        <v>108676184</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3698,7 +3423,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3711,17 +3436,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563482</v>
+        <v>563449</v>
       </c>
       <c r="R26" t="n">
-        <v>6575995</v>
+        <v>6576484</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3745,27 +3470,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Tvåhundra knärotsplantor inom yta av 5 kvm. Skogen är avverkningsanmäld. Ingen avgränsning eller skyddszon.</t>
+          <t>Tre knärotsplantor i sandtallskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3792,15 +3517,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115073086</v>
+        <v>108677391</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3827,7 +3547,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3840,14 +3560,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563487</v>
+        <v>563440</v>
       </c>
       <c r="R27" t="n">
-        <v>6576004</v>
+        <v>6576425</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3874,27 +3594,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Två plantor under senvuxen gran.</t>
+          <t>En planta, kanske flera i mossan. Sandtallskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3921,15 +3641,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115073720</v>
+        <v>108678257</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3956,26 +3671,30 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563478</v>
+        <v>563443</v>
       </c>
       <c r="R28" t="n">
-        <v>6576026</v>
+        <v>6576277</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3999,22 +3718,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växer under en samling senvuxna granar. Sandtallskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4041,15 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115072528</v>
+        <v>108678905</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4076,26 +3795,30 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563481</v>
+        <v>563435</v>
       </c>
       <c r="R29" t="n">
-        <v>6575990</v>
+        <v>6576265</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4119,22 +3842,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 80 plantor, troligen mer. Fuktig del av sandtallskog, med en samling senvuxna granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4161,15 +3889,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115077038</v>
+        <v>108679239</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4196,26 +3919,30 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563470</v>
+        <v>563429</v>
       </c>
       <c r="R30" t="n">
-        <v>6575978</v>
+        <v>6576248</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4239,22 +3966,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4281,15 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115124188</v>
+        <v>108679662</v>
       </c>
       <c r="B31" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4316,7 +4038,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4324,26 +4046,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ox-gömman, Srm</t>
+          <t>Västerdal, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563480</v>
+        <v>563419</v>
       </c>
       <c r="R31" t="n">
-        <v>6576027</v>
+        <v>6576243</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4367,27 +4085,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Trettio plantor i mossan och en med vinterståndare.</t>
+          <t>Många plantor som gömmer sig i mossan. Säkert fler än 45 knärot. Sandtallskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4414,15 +4132,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115125738</v>
+        <v>115045812</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4449,10 +4162,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4462,13 +4179,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563449</v>
+        <v>563455</v>
       </c>
       <c r="R32" t="n">
-        <v>6576003</v>
+        <v>6576283</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4492,27 +4209,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Knäroten växer alldeles intill stigen ”Björnlunken”. Ett motionsspår.</t>
+          <t>Ca trettio plantor 12 meter utanför Holmen skog AB s avgränsningar för knärot.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4539,15 +4256,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115125073</v>
+        <v>115046047</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4574,7 +4286,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4582,11 +4294,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4595,13 +4303,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563462</v>
+        <v>563451</v>
       </c>
       <c r="R33" t="n">
-        <v>6576127</v>
+        <v>6576290</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4625,22 +4333,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>20 knärot 15 m utanför Holmens skogs avgränsningar för växtplatser knärot.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4667,15 +4380,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115125472</v>
+        <v>115049490</v>
       </c>
       <c r="B34" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4700,12 +4408,12 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4715,10 +4423,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563447</v>
+        <v>563449</v>
       </c>
       <c r="R34" t="n">
-        <v>6576095</v>
+        <v>6576270</v>
       </c>
       <c r="S34" t="n">
         <v>2</v>
@@ -4745,22 +4453,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4787,15 +4495,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115180632</v>
+        <v>115049721</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4822,10 +4525,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4835,13 +4542,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563442</v>
+        <v>563452</v>
       </c>
       <c r="R35" t="n">
-        <v>6576032</v>
+        <v>6576326</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4865,22 +4572,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Holmen planerar avverka en knärotsskog. De här plantorna har inte avgränsats.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4907,15 +4619,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115123774</v>
+        <v>115049847</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,11 +4652,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4959,10 +4662,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563458</v>
+        <v>563446</v>
       </c>
       <c r="R36" t="n">
-        <v>6576009</v>
+        <v>6576328</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -4989,22 +4692,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5013,7 +4716,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5032,15 +4734,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115124786</v>
+        <v>115061053</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5067,14 +4764,10 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -5084,10 +4777,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563456</v>
+        <v>563423</v>
       </c>
       <c r="R37" t="n">
-        <v>6576135</v>
+        <v>6576253</v>
       </c>
       <c r="S37" t="n">
         <v>6</v>
@@ -5114,22 +4807,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett trettiotal knärotsplantor utanför Skogsstyrelsens avgränsningar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,7 +4836,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5154,6 +4851,2165 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115072402</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>563457</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6575978</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växer bredvid en nedsågad senvuxen gran i skuggigt läge. Skogen avverkningsanmäld.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115072528</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>563481</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6575990</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115072782</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>563482</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6575995</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tvåhundra knärotsplantor inom yta av 5 kvm. Skogen är avverkningsanmäld. Ingen avgränsning eller skyddszon.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115073086</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>563487</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6576004</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Två plantor under senvuxen gran.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115073720</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>563478</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6576026</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115074041</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>563472</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6575994</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115074228</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>563458</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6575996</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115075254</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>563436</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6575993</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115077038</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>563470</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6575978</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115123774</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>563458</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6576009</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>115124188</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>563480</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6576027</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Trettio plantor i mossan och en med vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>115124786</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>563456</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6576135</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>115125073</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>563462</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6576127</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>115125472</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>563447</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6576095</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115125738</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>563449</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6576003</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Knäroten växer alldeles intill stigen ”Björnlunken”. Ett motionsspår.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115180632</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>563442</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6576032</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>115181152</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>563423</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6576174</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>115819974</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ox-gömman, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>563429</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6576082</v>
+      </c>
+      <c r="S55" t="n">
+        <v>6</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10 knärotsplantor utanför skogsbolaget Holmens avgränsningar. Se bild.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17144-2023 artfynd.xlsx
+++ b/artfynd/A 17144-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96209026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104094718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96206087</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079434</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96209215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96379933</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104067617</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079418</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079433</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +2135,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079439</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2187,6 +2257,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111379535</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2295,6 +2370,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96379879</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2420,6 +2500,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108533341</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2540,6 +2625,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108535141</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2682,6 +2772,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108692909</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2783,6 +2878,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079417</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2907,6 +3007,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108534315</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3031,6 +3136,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108534864</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3146,6 +3256,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108535011</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3266,6 +3381,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108535895</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3390,6 +3510,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108675609</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3514,6 +3639,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108676184</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3638,6 +3768,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108677391</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3762,6 +3897,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108678257</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3886,6 +4026,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108678905</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4005,6 +4150,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108679239</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4129,6 +4279,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108679662</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4253,6 +4408,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045812</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4377,6 +4537,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115046047</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4492,6 +4657,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115049490</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4616,6 +4786,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115049721</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4731,6 +4906,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115049847</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4851,6 +5031,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115061053</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4975,6 +5160,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115072402</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5090,6 +5280,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115072528</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5214,6 +5409,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115072782</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5338,6 +5538,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115073086</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5453,6 +5658,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115073720</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5572,6 +5782,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115074041</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5691,6 +5906,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115074228</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5810,6 +6030,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115075254</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5925,6 +6150,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115077038</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6045,6 +6275,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115123774</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6173,6 +6408,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115124188</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6293,6 +6533,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115124786</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6416,6 +6661,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115125073</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6531,6 +6781,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115125472</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6651,6 +6906,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115125738</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6766,6 +7026,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115180632</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6886,6 +7151,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115181152</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7010,8 +7280,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115819974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>